--- a/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123422769</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570065</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570063</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570172</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,8 +1266,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569853</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123422769</v>
+        <v>136017254</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>56901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>208257</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,19 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fiversättra, Fiversättra, Srm</t>
+          <t>Norra skogen naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699151</v>
+        <v>699066</v>
       </c>
       <c r="R2" t="n">
-        <v>6554866</v>
+        <v>6554550</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:43</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tjäderspillning under gammal tall.</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,80 +764,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Ola Vestre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries</t>
+          <t>Ola Vestre, Trine Parmer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123422769</t>
+          <t>https://artportalen.se/Sighting/136017254</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125570065</v>
+        <v>123422769</v>
       </c>
       <c r="B3" t="n">
-        <v>111390</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kramsholmsudd, Srm</t>
+          <t>Fiversättra, Fiversättra, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699764</v>
+        <v>699151</v>
       </c>
       <c r="R3" t="n">
-        <v>6555040</v>
+        <v>6554866</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +853,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tjäderspillning under gammal tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,60 +884,61 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125570065</t>
+          <t>https://artportalen.se/Sighting/123422769</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125570063</v>
+        <v>125570065</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>111390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219711</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -1032,13 +1020,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125570063</t>
+          <t>https://artportalen.se/Sighting/125570065</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125570172</v>
+        <v>125570063</v>
       </c>
       <c r="B5" t="n">
         <v>99035</v>
@@ -1066,7 +1054,11 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1077,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699805</v>
+        <v>699764</v>
       </c>
       <c r="R5" t="n">
-        <v>6555031</v>
+        <v>6555040</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,16 +1140,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125570172</t>
+          <t>https://artportalen.se/Sighting/125570063</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125569853</v>
+        <v>125570172</v>
       </c>
       <c r="B6" t="n">
-        <v>99141</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,28 +1157,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1197,13 +1185,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699777</v>
+        <v>699805</v>
       </c>
       <c r="R6" t="n">
-        <v>6555004</v>
+        <v>6555031</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,6 +1255,126 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570172</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125569853</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kramsholmsudd, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>699777</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6555004</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125569853</t>
         </is>
@@ -1279,6 +1387,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136017254</v>
       </c>
       <c r="B2" t="n">
-        <v>56901</v>
+        <v>56903</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136017254</v>
       </c>
       <c r="B2" t="n">
-        <v>56903</v>
+        <v>56904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136017254</v>
       </c>
       <c r="B2" t="n">
-        <v>56904</v>
+        <v>56908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136017254</v>
       </c>
       <c r="B2" t="n">
-        <v>56908</v>
+        <v>56909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
+++ b/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136017254</v>
       </c>
       <c r="B2" t="n">
-        <v>56909</v>
+        <v>56914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
